--- a/templates/010101_X_X_NNN_PipelineWorksheet.xlsx
+++ b/templates/010101_X_X_NNN_PipelineWorksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\projects\alindsay\Projects\ngs-pipeline-launcher\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EC537D-A93A-42D3-9CB6-EB724015686B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF343F-7895-499B-A32A-20E75C237406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25920" yWindow="0" windowWidth="25785" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PipelineWorksheet" sheetId="1" r:id="rId1"/>
@@ -1452,7 +1452,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" style="1" customWidth="1"/>
     <col min="5" max="18" width="20.7109375" customWidth="1"/>
